--- a/data/2024/35-suceava/146263-suceava/budget_file.xlsx
+++ b/data/2024/35-suceava/146263-suceava/budget_file.xlsx
@@ -1086,7 +1086,7 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>07.02.01 est2027: parent 116.000.000,00 != sum(children) 90.000.000,00 (2 children); 07.02.01 est2026: parent 118.700.000,00 != sum(children) 90.000.000,00 (2 children); 07.02.01 total_2024: parent 139.644.400,00 != sum(children) 108.940.000,00 (2 children); 07.02.01 est2025: parent 116.700.000,00 != sum(children) 90.000.000,00 (2 children)</t>
+          <t>07.02.01 total_2024: parent 139.644.400,00 != sum(children) 108.940.000,00 (2 children); 07.02.01 est2025: parent 116.700.000,00 != sum(children) 90.000.000,00 (2 children); 07.02.01 est2027: parent 116.000.000,00 != sum(children) 90.000.000,00 (2 children); 07.02.01 est2026: parent 118.700.000,00 != sum(children) 90.000.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>07.02 est2027: parent 116.000.000,00 != sum(children) 142.000.000,00 (4 children); 07.02 est2026: parent 118.700.000,00 != sum(children) 147.400.000,00 (4 children); 07.02 total_2024: parent 139.644.400,00 != sum(children) 170.348.800,00 (4 children); 07.02 est2025: parent 116.700.000,00 != sum(children) 143.400.000,00 (4 children)</t>
+          <t>07.02 total_2024: parent 139.644.400,00 != sum(children) 170.348.800,00 (4 children); 07.02 est2025: parent 116.700.000,00 != sum(children) 143.400.000,00 (4 children); 07.02 est2027: parent 116.000.000,00 != sum(children) 142.000.000,00 (4 children); 07.02 est2026: parent 118.700.000,00 != sum(children) 147.400.000,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>11.02 est2027: parent 81.068.000,00 != sum(children) 232.936.000,00 (4 children); 11.02 est2026: parent 79.857.000,00 != sum(children) 235.514.000,00 (4 children); 11.02 total_2024: parent 101.356.000,00 != sum(children) 283.646.000,00 (4 children); 11.02 est2025: parent 78.541.000,00 != sum(children) 229.882.000,00 (4 children)</t>
+          <t>11.02 total_2024: parent 101.356.000,00 != sum(children) 283.646.000,00 (4 children); 11.02 est2025: parent 78.541.000,00 != sum(children) 229.882.000,00 (4 children); 11.02 est2027: parent 81.068.000,00 != sum(children) 232.936.000,00 (4 children); 11.02 est2026: parent 79.857.000,00 != sum(children) 235.514.000,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>30.02 est2027: parent 36.760.360,00 != sum(children) 131.470.720,00 (3 children); 30.02 est2026: parent 36.000.000,00 != sum(children) 140.339.130,00 (3 children); 30.02 total_2024: parent 52.280.000,00 != sum(children) 207.069.620,00 (3 children); 30.02 est2025: parent 33.626.120,00 != sum(children) 132.852.240,00 (3 children)</t>
+          <t>30.02 total_2024: parent 52.280.000,00 != sum(children) 207.069.620,00 (3 children); 30.02 est2025: parent 33.626.120,00 != sum(children) 132.852.240,00 (3 children); 30.02 est2027: parent 36.760.360,00 != sum(children) 131.470.720,00 (3 children); 30.02 est2026: parent 36.000.000,00 != sum(children) 140.339.130,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>07.02.01 est2027: parent 116.000.000,00 != sum(children) 90.000.000,00 (2 children); 07.02.01 est2026: parent 118.700.000,00 != sum(children) 90.000.000,00 (2 children); 07.02.01 total_2024: parent 139.644.400,00 != sum(children) 108.940.000,00 (2 children); 07.02.01 est2025: parent 116.700.000,00 != sum(children) 90.000.000,00 (2 children)</t>
+          <t>07.02.01 total_2024: parent 139.644.400,00 != sum(children) 108.940.000,00 (2 children); 07.02.01 est2025: parent 116.700.000,00 != sum(children) 90.000.000,00 (2 children); 07.02.01 est2027: parent 116.000.000,00 != sum(children) 90.000.000,00 (2 children); 07.02.01 est2026: parent 118.700.000,00 != sum(children) 90.000.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>07.02 est2027: parent 116.000.000,00 != sum(children) 142.000.000,00 (4 children); 07.02 est2026: parent 118.700.000,00 != sum(children) 147.400.000,00 (4 children); 07.02 total_2024: parent 139.644.400,00 != sum(children) 170.348.800,00 (4 children); 07.02 est2025: parent 116.700.000,00 != sum(children) 143.400.000,00 (4 children)</t>
+          <t>07.02 total_2024: parent 139.644.400,00 != sum(children) 170.348.800,00 (4 children); 07.02 est2025: parent 116.700.000,00 != sum(children) 143.400.000,00 (4 children); 07.02 est2027: parent 116.000.000,00 != sum(children) 142.000.000,00 (4 children); 07.02 est2026: parent 118.700.000,00 != sum(children) 147.400.000,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>11.02 est2027: parent 81.068.000,00 != sum(children) 232.936.000,00 (4 children); 11.02 est2026: parent 79.857.000,00 != sum(children) 235.514.000,00 (4 children); 11.02 total_2024: parent 101.356.000,00 != sum(children) 283.646.000,00 (4 children); 11.02 est2025: parent 78.541.000,00 != sum(children) 229.882.000,00 (4 children)</t>
+          <t>11.02 total_2024: parent 101.356.000,00 != sum(children) 283.646.000,00 (4 children); 11.02 est2025: parent 78.541.000,00 != sum(children) 229.882.000,00 (4 children); 11.02 est2027: parent 81.068.000,00 != sum(children) 232.936.000,00 (4 children); 11.02 est2026: parent 79.857.000,00 != sum(children) 235.514.000,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>30.02 est2027: parent 36.760.360,00 != sum(children) 79.707.680,00 (3 children); 30.02 est2026: parent 36.000.000,00 != sum(children) 61.521.740,00 (3 children); 30.02 total_2024: parent 52.280.000,00 != sum(children) 12.165.560,00 (3 children); 30.02 est2025: parent 33.626.120,00 != sum(children) 45.539.240,00 (3 children)</t>
+          <t>30.02 total_2024: parent 52.280.000,00 != sum(children) 12.165.560,00 (3 children); 30.02 est2025: parent 33.626.120,00 != sum(children) 45.539.240,00 (3 children); 30.02 est2027: parent 36.760.360,00 != sum(children) 79.707.680,00 (3 children); 30.02 est2026: parent 36.000.000,00 != sum(children) 61.521.740,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -5567,7 +5567,7 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Varsaminte din sectiunea de functionare pentru finantarea sectiunii de dezvoltare a bugetelui local</t>
         </is>
@@ -5578,11 +5578,7 @@
       <c r="E2" t="n">
         <v>5</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>annex</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" s="3" t="n">
         <v>-194904060</v>
       </c>
@@ -5603,7 +5599,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Varsaminte din sectiunea de functionare</t>
         </is>
@@ -5614,11 +5610,7 @@
       <c r="E3" t="n">
         <v>5</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>annex</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" s="3" t="n">
         <v>194904060</v>
       </c>
@@ -5765,7 +5757,7 @@
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>42.02 est2027: parent 16.317.400,00 != sum(children) 32.634.800,00 (9 children); 42.02 est2026: parent 27.763.360,00 != sum(children) 55.526.720,00 (9 children); 42.02 total_2024: parent 364.653.650,00 != sum(children) 795.203.990,00 (9 children); 42.02 est2025: parent 57.829.760,00 != sum(children) 115.659.520,00 (9 children)</t>
+          <t>42.02 total_2024: parent 364.653.650,00 != sum(children) 795.203.990,00 (9 children); 42.02 est2025: parent 57.829.760,00 != sum(children) 115.659.520,00 (9 children); 42.02 est2027: parent 16.317.400,00 != sum(children) 32.634.800,00 (9 children); 42.02 est2026: parent 27.763.360,00 != sum(children) 55.526.720,00 (9 children)</t>
         </is>
       </c>
     </row>
@@ -6836,7 +6828,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>TOTAL CHELTUIELI</t>
         </is>
@@ -6847,11 +6839,7 @@
       <c r="E33" t="n">
         <v>8</v>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>annex</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" s="3" t="n">
         <v>1069740090</v>
       </c>
@@ -13263,7 +13251,7 @@
       </c>
       <c r="M166" s="5" t="inlineStr">
         <is>
-          <t>51.02 total_2024: parent 42.267.300,00 != sum(children) 2.786.740,00 (1 children); 51.02 est2026: parent 46.504.310,00 != sum(children) 3.037.360,00 (1 children); 51.02 est2025: parent 44.319.960,00 != sum(children) 2.903.790,00 (1 children); 51.02 est2027: parent 48.755.070,00 != sum(children) 3.161.890,00 (1 children)</t>
+          <t>51.02 est2027: parent 48.755.070,00 != sum(children) 3.161.890,00 (1 children); 51.02 est2025: parent 44.319.960,00 != sum(children) 2.903.790,00 (1 children); 51.02 total_2024: parent 42.267.300,00 != sum(children) 2.786.740,00 (1 children); 51.02 est2026: parent 46.504.310,00 != sum(children) 3.037.360,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -18364,7 +18352,7 @@
       </c>
       <c r="M264" s="5" t="inlineStr">
         <is>
-          <t>61.02 credite_restante: parent 725.965,00 != sum(children) 88.684,00 (1 children); 61.02 total_2024: parent 16.553.660,00 != sum(children) 531.500,00 (1 children); 61.02 est2026: parent 18.042.320,00 != sum(children) 579.290,00 (1 children); 61.02 est2025: parent 17.248.930,00 != sum(children) 553.800,00 (1 children); 61.02 est2027: parent 18.781.950,00 != sum(children) 603.000,00 (1 children)</t>
+          <t>61.02 est2027: parent 18.781.950,00 != sum(children) 603.000,00 (1 children); 61.02 credite_restante: parent 725.965,00 != sum(children) 88.684,00 (1 children); 61.02 est2025: parent 17.248.930,00 != sum(children) 553.800,00 (1 children); 61.02 total_2024: parent 16.553.660,00 != sum(children) 531.500,00 (1 children); 61.02 est2026: parent 18.042.320,00 != sum(children) 579.290,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -20980,7 +20968,7 @@
       </c>
       <c r="M314" s="5" t="inlineStr">
         <is>
-          <t>65.02 credite_restante: parent 15.894.477,00 != sum(children) 9.061.759,00 (1 children); 65.02 total_2024: parent 208.787.350,00 != sum(children) 26.330.710,00 (1 children); 65.02 est2026: parent 134.900.670,00 != sum(children) 6.416.200,00 (1 children); 65.02 est2025: parent 131.665.700,00 != sum(children) 6.353.900,00 (1 children); 65.02 est2027: parent 114.763.210,00 != sum(children) 2.474.200,00 (1 children)</t>
+          <t>65.02 est2027: parent 114.763.210,00 != sum(children) 2.474.200,00 (1 children); 65.02 credite_restante: parent 15.894.477,00 != sum(children) 9.061.759,00 (1 children); 65.02 est2025: parent 131.665.700,00 != sum(children) 6.353.900,00 (1 children); 65.02 total_2024: parent 208.787.350,00 != sum(children) 26.330.710,00 (1 children); 65.02 est2026: parent 134.900.670,00 != sum(children) 6.416.200,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -27207,7 +27195,7 @@
       </c>
       <c r="M434" s="5" t="inlineStr">
         <is>
-          <t>67.02 credite_restante: parent 5.080.830,00 != sum(children) 1.023.756,00 (2 children); 67.02 total_2024: parent 76.184.020,00 != sum(children) 13.725.000,00 (2 children); 67.02 est2025: parent 116.207.800,00 != sum(children) 1.348.000,00 (2 children)</t>
+          <t>67.02 credite_restante: parent 5.080.830,00 != sum(children) 1.023.756,00 (2 children); 67.02 est2025: parent 116.207.800,00 != sum(children) 1.348.000,00 (2 children); 67.02 total_2024: parent 76.184.020,00 != sum(children) 13.725.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -34543,7 +34531,7 @@
       </c>
       <c r="M576" s="5" t="inlineStr">
         <is>
-          <t>70.02 credite_restante: parent 12.813.202,00 != sum(children) 9.047.355,00 (1 children); 70.02 total_2024: parent 163.510.420,00 != sum(children) 54.059.300,00 (1 children); 70.02 est2026: parent 53.130.830,00 != sum(children) 10.600.000,00 (1 children); 70.02 est2025: parent 64.492.730,00 != sum(children) 20.788.000,00 (1 children); 70.02 est2027: parent 53.431.400,00 != sum(children) 10.900.000,00 (1 children)</t>
+          <t>70.02 est2027: parent 53.431.400,00 != sum(children) 10.900.000,00 (1 children); 70.02 credite_restante: parent 12.813.202,00 != sum(children) 9.047.355,00 (1 children); 70.02 est2025: parent 64.492.730,00 != sum(children) 20.788.000,00 (1 children); 70.02 total_2024: parent 163.510.420,00 != sum(children) 54.059.300,00 (1 children); 70.02 est2026: parent 53.130.830,00 != sum(children) 10.600.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -37492,7 +37480,7 @@
       </c>
       <c r="M633" s="5" t="inlineStr">
         <is>
-          <t>74.02 credite_restante: parent 11.932.165,00 != sum(children) 128.560,00 (2 children); 74.02 total_2024: parent 72.043.920,00 != sum(children) 4.015.000,00 (2 children); 74.02 est2026: parent 57.479.480,00 != sum(children) 2.215.000,00 (2 children); 74.02 est2025: parent 55.232.880,00 != sum(children) 2.215.000,00 (2 children); 74.02 est2027: parent 59.716.480,00 != sum(children) 2.215.000,00 (2 children)</t>
+          <t>74.02 est2027: parent 59.716.480,00 != sum(children) 2.215.000,00 (2 children); 74.02 credite_restante: parent 11.932.165,00 != sum(children) 128.560,00 (2 children); 74.02 est2025: parent 55.232.880,00 != sum(children) 2.215.000,00 (2 children); 74.02 total_2024: parent 72.043.920,00 != sum(children) 4.015.000,00 (2 children); 74.02 est2026: parent 57.479.480,00 != sum(children) 2.215.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -41339,7 +41327,7 @@
       </c>
       <c r="M708" s="5" t="inlineStr">
         <is>
-          <t>81.02 total_2024: parent 98.079.410,00 != sum(children) 88.079.410,00 (2 children); 81.02 est2026: parent 40.698.000,00 != sum(children) 5.698.000,00 (2 children); 81.02 est2025: parent 35.698.000,00 != sum(children) 5.698.000,00 (2 children); 81.02 est2027: parent 45.698.000,00 != sum(children) 5.698.000,00 (2 children)</t>
+          <t>81.02 est2027: parent 45.698.000,00 != sum(children) 5.698.000,00 (2 children); 81.02 est2025: parent 35.698.000,00 != sum(children) 5.698.000,00 (2 children); 81.02 total_2024: parent 98.079.410,00 != sum(children) 88.079.410,00 (2 children); 81.02 est2026: parent 40.698.000,00 != sum(children) 5.698.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -42249,7 +42237,7 @@
       </c>
       <c r="M726" s="5" t="inlineStr">
         <is>
-          <t>84.02 credite_restante: parent 11.716.680,00 != sum(children) 1.090.648,00 (2 children); 84.02 total_2024: parent 287.514.870,00 != sum(children) 104.449.550,00 (2 children); 84.02 est2026: parent 171.033.080,00 != sum(children) 35.834.000,00 (2 children); 84.02 est2025: parent 180.384.190,00 != sum(children) 34.340.000,00 (2 children); 84.02 est2027: parent 145.921.210,00 != sum(children) 12.948.000,00 (2 children)</t>
+          <t>84.02 est2027: parent 145.921.210,00 != sum(children) 12.948.000,00 (2 children); 84.02 credite_restante: parent 11.716.680,00 != sum(children) 1.090.648,00 (2 children); 84.02 est2025: parent 180.384.190,00 != sum(children) 34.340.000,00 (2 children); 84.02 total_2024: parent 287.514.870,00 != sum(children) 104.449.550,00 (2 children); 84.02 est2026: parent 171.033.080,00 != sum(children) 35.834.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -44918,12 +44906,12 @@
       </c>
       <c r="M779" s="5" t="inlineStr">
         <is>
-          <t>99.02 credite_restante: parent 0,00 != sum(children) 21.109.182,00 (1 children); 99.02 total_2024: parent 400.030,00 != sum(children) 271.389.710,00 (1 children); 99.02 est2026: parent 0,00 != sum(children) 39.012.850,00 (1 children); 99.02 est2025: parent 0,00 != sum(children) 52.208.490,00 (1 children); 99.02 est2027: parent 0,00 != sum(children) 17.439.090,00 (1 children)</t>
+          <t>99.02 est2027: parent 0,00 != sum(children) 17.439.090,00 (1 children); 99.02 credite_restante: parent 0,00 != sum(children) 21.109.182,00 (1 children); 99.02 est2025: parent 0,00 != sum(children) 52.208.490,00 (1 children); 99.02 total_2024: parent 400.030,00 != sum(children) 271.389.710,00 (1 children); 99.02 est2026: parent 0,00 != sum(children) 39.012.850,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="780" ht="30" customHeight="1">
-      <c r="C780" s="4" t="inlineStr">
+      <c r="C780" s="2" t="inlineStr">
         <is>
           <t>Varsaminte din sectiunea de functionare pentru finantarea sectiunii de dezvoltare a bugetelui local</t>
         </is>
@@ -44934,11 +44922,7 @@
       <c r="E780" t="n">
         <v>59</v>
       </c>
-      <c r="F780" t="inlineStr">
-        <is>
-          <t>annex</t>
-        </is>
-      </c>
+      <c r="F780" t="inlineStr"/>
       <c r="G780" s="3" t="n">
         <v>-194904060</v>
       </c>
@@ -45085,7 +45069,7 @@
       </c>
       <c r="M783" s="5" t="inlineStr">
         <is>
-          <t>42.02 est2027: parent 7.317.400,00 != sum(children) 14.634.800,00 (4 children); 42.02 est2026: parent 7.033.200,00 != sum(children) 14.066.400,00 (4 children); 42.02 total_2024: parent 6.414.810,00 != sum(children) 12.829.620,00 (4 children); 42.02 est2025: parent 6.728.300,00 != sum(children) 13.456.600,00 (4 children)</t>
+          <t>42.02 total_2024: parent 6.414.810,00 != sum(children) 12.829.620,00 (4 children); 42.02 est2025: parent 6.728.300,00 != sum(children) 13.456.600,00 (4 children); 42.02 est2027: parent 7.317.400,00 != sum(children) 14.634.800,00 (4 children); 42.02 est2026: parent 7.033.200,00 != sum(children) 14.066.400,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -45213,7 +45197,7 @@
       </c>
     </row>
     <row r="787">
-      <c r="C787" s="4" t="inlineStr">
+      <c r="C787" s="2" t="inlineStr">
         <is>
           <t>TOTAL CHELTUIELI</t>
         </is>
@@ -45224,11 +45208,7 @@
       <c r="E787" t="n">
         <v>60</v>
       </c>
-      <c r="F787" t="inlineStr">
-        <is>
-          <t>annex</t>
-        </is>
-      </c>
+      <c r="F787" t="inlineStr"/>
       <c r="G787" s="3" t="n">
         <v>419559770</v>
       </c>
@@ -62007,7 +61987,7 @@
       </c>
       <c r="M1108" s="5" t="inlineStr">
         <is>
-          <t>67.02 total_2024: parent 53.899.470,00 != sum(children) 1.360.000,00 (1 children); 67.02 est2025: parent 50.625.000,00 != sum(children) 1.348.000,00 (1 children)</t>
+          <t>67.02 est2025: parent 50.625.000,00 != sum(children) 1.348.000,00 (1 children); 67.02 total_2024: parent 53.899.470,00 != sum(children) 1.360.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -69497,7 +69477,7 @@
       </c>
       <c r="M1253" s="5" t="inlineStr">
         <is>
-          <t>74.02 total_2024: parent 49.503.480,00 != sum(children) 2.400.000,00 (1 children); 74.02 est2026: parent 56.775.000,00 != sum(children) 2.215.000,00 (1 children); 74.02 est2025: parent 54.376.000,00 != sum(children) 2.215.000,00 (1 children); 74.02 est2027: parent 59.012.000,00 != sum(children) 2.215.000,00 (1 children)</t>
+          <t>74.02 est2027: parent 59.012.000,00 != sum(children) 2.215.000,00 (1 children); 74.02 est2025: parent 54.376.000,00 != sum(children) 2.215.000,00 (1 children); 74.02 total_2024: parent 49.503.480,00 != sum(children) 2.400.000,00 (1 children); 74.02 est2026: parent 56.775.000,00 != sum(children) 2.215.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -71244,7 +71224,7 @@
       </c>
       <c r="M1287" s="5" t="inlineStr">
         <is>
-          <t>81.02 total_2024: parent 16.350.000,00 != sum(children) 6.350.000,00 (1 children); 81.02 est2026: parent 40.698.000,00 != sum(children) 5.698.000,00 (1 children); 81.02 est2025: parent 35.698.000,00 != sum(children) 5.698.000,00 (1 children); 81.02 est2027: parent 45.698.000,00 != sum(children) 5.698.000,00 (1 children)</t>
+          <t>81.02 est2027: parent 45.698.000,00 != sum(children) 5.698.000,00 (1 children); 81.02 est2025: parent 35.698.000,00 != sum(children) 5.698.000,00 (1 children); 81.02 total_2024: parent 16.350.000,00 != sum(children) 6.350.000,00 (1 children); 81.02 est2026: parent 40.698.000,00 != sum(children) 5.698.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -71842,7 +71822,7 @@
       </c>
       <c r="M1299" s="5" t="inlineStr">
         <is>
-          <t>84.02 total_2024: parent 62.961.130,00 != sum(children) 12.820.000,00 (1 children); 84.02 est2026: parent 104.603.000,00 != sum(children) 17.454.000,00 (1 children); 84.02 est2025: parent 95.741.700,00 != sum(children) 12.731.000,00 (1 children); 84.02 est2027: parent 103.926.300,00 != sum(children) 12.648.000,00 (1 children)</t>
+          <t>84.02 est2027: parent 103.926.300,00 != sum(children) 12.648.000,00 (1 children); 84.02 est2025: parent 95.741.700,00 != sum(children) 12.731.000,00 (1 children); 84.02 total_2024: parent 62.961.130,00 != sum(children) 12.820.000,00 (1 children); 84.02 est2026: parent 104.603.000,00 != sum(children) 17.454.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -73192,12 +73172,12 @@
       </c>
       <c r="M1326" s="5" t="inlineStr">
         <is>
-          <t>99.02 total_2024: parent 0,00 != sum(children) 22.930.000,00 (1 children); 99.02 est2026: parent 0,00 != sum(children) 25.367.000,00 (1 children); 99.02 est2025: parent 0,00 != sum(children) 21.992.000,00 (1 children); 99.02 est2027: parent 0,00 != sum(children) 20.561.000,00 (1 children)</t>
+          <t>99.02 est2027: parent 0,00 != sum(children) 20.561.000,00 (1 children); 99.02 est2025: parent 0,00 != sum(children) 21.992.000,00 (1 children); 99.02 total_2024: parent 0,00 != sum(children) 22.930.000,00 (1 children); 99.02 est2026: parent 0,00 != sum(children) 25.367.000,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="1327">
-      <c r="C1327" s="4" t="inlineStr">
+      <c r="C1327" s="2" t="inlineStr">
         <is>
           <t>Varsaminte din sectiunea de functionare</t>
         </is>
@@ -73208,11 +73188,7 @@
       <c r="E1327" t="n">
         <v>92</v>
       </c>
-      <c r="F1327" t="inlineStr">
-        <is>
-          <t>annex</t>
-        </is>
-      </c>
+      <c r="F1327" t="inlineStr"/>
       <c r="G1327" s="3" t="n">
         <v>194904060</v>
       </c>
@@ -74307,7 +74283,7 @@
       </c>
     </row>
     <row r="1354">
-      <c r="C1354" s="4" t="inlineStr">
+      <c r="C1354" s="2" t="inlineStr">
         <is>
           <t>TOTAL CHELTUIELI</t>
         </is>
@@ -74318,11 +74294,7 @@
       <c r="E1354" t="n">
         <v>94</v>
       </c>
-      <c r="F1354" t="inlineStr">
-        <is>
-          <t>annex</t>
-        </is>
-      </c>
+      <c r="F1354" t="inlineStr"/>
       <c r="G1354" s="3" t="n">
         <v>650180320</v>
       </c>
@@ -88342,12 +88314,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>07.02.01 est2027: parent 116.000.000,00 != sum(children) 90.000.000,00 (2 children)</t>
+          <t>07.02.01 total_2024: parent 139.644.400,00 != sum(children) 108.940.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -88372,12 +88344,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>est2025</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>07.02.01 est2026: parent 118.700.000,00 != sum(children) 90.000.000,00 (2 children)</t>
+          <t>07.02.01 est2025: parent 116.700.000,00 != sum(children) 90.000.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -88402,12 +88374,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>07.02.01 total_2024: parent 139.644.400,00 != sum(children) 108.940.000,00 (2 children)</t>
+          <t>07.02.01 est2027: parent 116.000.000,00 != sum(children) 90.000.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -88432,12 +88404,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>est2025</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>07.02.01 est2025: parent 116.700.000,00 != sum(children) 90.000.000,00 (2 children)</t>
+          <t>07.02.01 est2026: parent 118.700.000,00 != sum(children) 90.000.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -88462,12 +88434,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>07.02 est2027: parent 116.000.000,00 != sum(children) 142.000.000,00 (4 children)</t>
+          <t>07.02 total_2024: parent 139.644.400,00 != sum(children) 170.348.800,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -88492,12 +88464,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>est2025</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>07.02 est2026: parent 118.700.000,00 != sum(children) 147.400.000,00 (4 children)</t>
+          <t>07.02 est2025: parent 116.700.000,00 != sum(children) 143.400.000,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -88522,12 +88494,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>07.02 total_2024: parent 139.644.400,00 != sum(children) 170.348.800,00 (4 children)</t>
+          <t>07.02 est2027: parent 116.000.000,00 != sum(children) 142.000.000,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -88552,12 +88524,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>est2025</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>07.02 est2025: parent 116.700.000,00 != sum(children) 143.400.000,00 (4 children)</t>
+          <t>07.02 est2026: parent 118.700.000,00 != sum(children) 147.400.000,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -88632,12 +88604,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>11.02 est2027: parent 81.068.000,00 != sum(children) 232.936.000,00 (4 children)</t>
+          <t>11.02 total_2024: parent 101.356.000,00 != sum(children) 283.646.000,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -88662,12 +88634,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>est2025</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>11.02 est2026: parent 79.857.000,00 != sum(children) 235.514.000,00 (4 children)</t>
+          <t>11.02 est2025: parent 78.541.000,00 != sum(children) 229.882.000,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -88692,12 +88664,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>11.02 total_2024: parent 101.356.000,00 != sum(children) 283.646.000,00 (4 children)</t>
+          <t>11.02 est2027: parent 81.068.000,00 != sum(children) 232.936.000,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -88722,12 +88694,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>est2025</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>11.02 est2025: parent 78.541.000,00 != sum(children) 229.882.000,00 (4 children)</t>
+          <t>11.02 est2026: parent 79.857.000,00 != sum(children) 235.514.000,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -88802,12 +88774,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>30.02 est2027: parent 36.760.360,00 != sum(children) 131.470.720,00 (3 children)</t>
+          <t>30.02 total_2024: parent 52.280.000,00 != sum(children) 207.069.620,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -88832,12 +88804,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>est2025</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>30.02 est2026: parent 36.000.000,00 != sum(children) 140.339.130,00 (3 children)</t>
+          <t>30.02 est2025: parent 33.626.120,00 != sum(children) 132.852.240,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -88862,12 +88834,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>30.02 total_2024: parent 52.280.000,00 != sum(children) 207.069.620,00 (3 children)</t>
+          <t>30.02 est2027: parent 36.760.360,00 != sum(children) 131.470.720,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -88892,12 +88864,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>est2025</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>30.02 est2025: parent 33.626.120,00 != sum(children) 132.852.240,00 (3 children)</t>
+          <t>30.02 est2026: parent 36.000.000,00 != sum(children) 140.339.130,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -88972,12 +88944,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>42.02 est2027: parent 16.317.400,00 != sum(children) 32.634.800,00 (9 children)</t>
+          <t>42.02 total_2024: parent 364.653.650,00 != sum(children) 795.203.990,00 (9 children)</t>
         </is>
       </c>
     </row>
@@ -89002,12 +88974,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>est2025</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>42.02 est2026: parent 27.763.360,00 != sum(children) 55.526.720,00 (9 children)</t>
+          <t>42.02 est2025: parent 57.829.760,00 != sum(children) 115.659.520,00 (9 children)</t>
         </is>
       </c>
     </row>
@@ -89032,12 +89004,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>42.02 total_2024: parent 364.653.650,00 != sum(children) 795.203.990,00 (9 children)</t>
+          <t>42.02 est2027: parent 16.317.400,00 != sum(children) 32.634.800,00 (9 children)</t>
         </is>
       </c>
     </row>
@@ -89062,12 +89034,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>est2025</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>42.02 est2025: parent 57.829.760,00 != sum(children) 115.659.520,00 (9 children)</t>
+          <t>42.02 est2026: parent 27.763.360,00 != sum(children) 55.526.720,00 (9 children)</t>
         </is>
       </c>
     </row>
@@ -89092,12 +89064,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>51.02 total_2024: parent 42.267.300,00 != sum(children) 2.786.740,00 (1 children)</t>
+          <t>51.02 est2027: parent 48.755.070,00 != sum(children) 3.161.890,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -89122,12 +89094,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>est2025</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>51.02 est2026: parent 46.504.310,00 != sum(children) 3.037.360,00 (1 children)</t>
+          <t>51.02 est2025: parent 44.319.960,00 != sum(children) 2.903.790,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -89152,12 +89124,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>est2025</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>51.02 est2025: parent 44.319.960,00 != sum(children) 2.903.790,00 (1 children)</t>
+          <t>51.02 total_2024: parent 42.267.300,00 != sum(children) 2.786.740,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -89182,12 +89154,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>51.02 est2027: parent 48.755.070,00 != sum(children) 3.161.890,00 (1 children)</t>
+          <t>51.02 est2026: parent 46.504.310,00 != sum(children) 3.037.360,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -89317,12 +89289,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>credite_restante</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.02 credite_restante: parent 725.965,00 != sum(children) 88.684,00 (1 children)</t>
+          <t>61.02 est2027: parent 18.781.950,00 != sum(children) 603.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -89347,12 +89319,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>credite_restante</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.02 total_2024: parent 16.553.660,00 != sum(children) 531.500,00 (1 children)</t>
+          <t>61.02 credite_restante: parent 725.965,00 != sum(children) 88.684,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -89377,12 +89349,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>est2025</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.02 est2026: parent 18.042.320,00 != sum(children) 579.290,00 (1 children)</t>
+          <t>61.02 est2025: parent 17.248.930,00 != sum(children) 553.800,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -89407,12 +89379,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>est2025</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.02 est2025: parent 17.248.930,00 != sum(children) 553.800,00 (1 children)</t>
+          <t>61.02 total_2024: parent 16.553.660,00 != sum(children) 531.500,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -89437,12 +89409,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.02 est2027: parent 18.781.950,00 != sum(children) 603.000,00 (1 children)</t>
+          <t>61.02 est2026: parent 18.042.320,00 != sum(children) 579.290,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -89492,12 +89464,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>credite_restante</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>65.02 credite_restante: parent 15.894.477,00 != sum(children) 9.061.759,00 (1 children)</t>
+          <t>65.02 est2027: parent 114.763.210,00 != sum(children) 2.474.200,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -89522,12 +89494,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>credite_restante</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>65.02 total_2024: parent 208.787.350,00 != sum(children) 26.330.710,00 (1 children)</t>
+          <t>65.02 credite_restante: parent 15.894.477,00 != sum(children) 9.061.759,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -89552,12 +89524,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>est2025</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>65.02 est2026: parent 134.900.670,00 != sum(children) 6.416.200,00 (1 children)</t>
+          <t>65.02 est2025: parent 131.665.700,00 != sum(children) 6.353.900,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -89582,12 +89554,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>est2025</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>65.02 est2025: parent 131.665.700,00 != sum(children) 6.353.900,00 (1 children)</t>
+          <t>65.02 total_2024: parent 208.787.350,00 != sum(children) 26.330.710,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -89612,12 +89584,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>65.02 est2027: parent 114.763.210,00 != sum(children) 2.474.200,00 (1 children)</t>
+          <t>65.02 est2026: parent 134.900.670,00 != sum(children) 6.416.200,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -89722,12 +89694,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2025</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>67.02 total_2024: parent 76.184.020,00 != sum(children) 13.725.000,00 (2 children)</t>
+          <t>67.02 est2025: parent 116.207.800,00 != sum(children) 1.348.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -89752,12 +89724,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>est2025</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>67.02 est2025: parent 116.207.800,00 != sum(children) 1.348.000,00 (2 children)</t>
+          <t>67.02 total_2024: parent 76.184.020,00 != sum(children) 13.725.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -89892,12 +89864,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>credite_restante</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>70.02 credite_restante: parent 12.813.202,00 != sum(children) 9.047.355,00 (1 children)</t>
+          <t>70.02 est2027: parent 53.431.400,00 != sum(children) 10.900.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -89922,12 +89894,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>credite_restante</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>70.02 total_2024: parent 163.510.420,00 != sum(children) 54.059.300,00 (1 children)</t>
+          <t>70.02 credite_restante: parent 12.813.202,00 != sum(children) 9.047.355,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -89952,12 +89924,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>est2025</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>70.02 est2026: parent 53.130.830,00 != sum(children) 10.600.000,00 (1 children)</t>
+          <t>70.02 est2025: parent 64.492.730,00 != sum(children) 20.788.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -89982,12 +89954,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>est2025</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>70.02 est2025: parent 64.492.730,00 != sum(children) 20.788.000,00 (1 children)</t>
+          <t>70.02 total_2024: parent 163.510.420,00 != sum(children) 54.059.300,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -90012,12 +89984,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>70.02 est2027: parent 53.431.400,00 != sum(children) 10.900.000,00 (1 children)</t>
+          <t>70.02 est2026: parent 53.130.830,00 != sum(children) 10.600.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -90067,12 +90039,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>credite_restante</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>74.02 credite_restante: parent 11.932.165,00 != sum(children) 128.560,00 (2 children)</t>
+          <t>74.02 est2027: parent 59.716.480,00 != sum(children) 2.215.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -90097,12 +90069,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>credite_restante</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>74.02 total_2024: parent 72.043.920,00 != sum(children) 4.015.000,00 (2 children)</t>
+          <t>74.02 credite_restante: parent 11.932.165,00 != sum(children) 128.560,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -90127,12 +90099,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>est2025</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>74.02 est2026: parent 57.479.480,00 != sum(children) 2.215.000,00 (2 children)</t>
+          <t>74.02 est2025: parent 55.232.880,00 != sum(children) 2.215.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -90157,12 +90129,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>est2025</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>74.02 est2025: parent 55.232.880,00 != sum(children) 2.215.000,00 (2 children)</t>
+          <t>74.02 total_2024: parent 72.043.920,00 != sum(children) 4.015.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -90187,12 +90159,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>74.02 est2027: parent 59.716.480,00 != sum(children) 2.215.000,00 (2 children)</t>
+          <t>74.02 est2026: parent 57.479.480,00 != sum(children) 2.215.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -90267,12 +90239,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>81.02 total_2024: parent 98.079.410,00 != sum(children) 88.079.410,00 (2 children)</t>
+          <t>81.02 est2027: parent 45.698.000,00 != sum(children) 5.698.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -90297,12 +90269,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>est2025</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>81.02 est2026: parent 40.698.000,00 != sum(children) 5.698.000,00 (2 children)</t>
+          <t>81.02 est2025: parent 35.698.000,00 != sum(children) 5.698.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -90327,12 +90299,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>est2025</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>81.02 est2025: parent 35.698.000,00 != sum(children) 5.698.000,00 (2 children)</t>
+          <t>81.02 total_2024: parent 98.079.410,00 != sum(children) 88.079.410,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -90357,12 +90329,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>81.02 est2027: parent 45.698.000,00 != sum(children) 5.698.000,00 (2 children)</t>
+          <t>81.02 est2026: parent 40.698.000,00 != sum(children) 5.698.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -90412,12 +90384,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>credite_restante</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>84.02 credite_restante: parent 11.716.680,00 != sum(children) 1.090.648,00 (2 children)</t>
+          <t>84.02 est2027: parent 145.921.210,00 != sum(children) 12.948.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -90442,12 +90414,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>credite_restante</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>84.02 total_2024: parent 287.514.870,00 != sum(children) 104.449.550,00 (2 children)</t>
+          <t>84.02 credite_restante: parent 11.716.680,00 != sum(children) 1.090.648,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -90472,12 +90444,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>est2025</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>84.02 est2026: parent 171.033.080,00 != sum(children) 35.834.000,00 (2 children)</t>
+          <t>84.02 est2025: parent 180.384.190,00 != sum(children) 34.340.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -90502,12 +90474,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>est2025</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>84.02 est2025: parent 180.384.190,00 != sum(children) 34.340.000,00 (2 children)</t>
+          <t>84.02 total_2024: parent 287.514.870,00 != sum(children) 104.449.550,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -90532,12 +90504,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>84.02 est2027: parent 145.921.210,00 != sum(children) 12.948.000,00 (2 children)</t>
+          <t>84.02 est2026: parent 171.033.080,00 != sum(children) 35.834.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -90612,12 +90584,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>credite_restante</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>99.02 credite_restante: parent 0,00 != sum(children) 21.109.182,00 (1 children)</t>
+          <t>99.02 est2027: parent 0,00 != sum(children) 17.439.090,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -90642,12 +90614,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>credite_restante</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>99.02 total_2024: parent 400.030,00 != sum(children) 271.389.710,00 (1 children)</t>
+          <t>99.02 credite_restante: parent 0,00 != sum(children) 21.109.182,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -90672,12 +90644,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>est2025</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>99.02 est2026: parent 0,00 != sum(children) 39.012.850,00 (1 children)</t>
+          <t>99.02 est2025: parent 0,00 != sum(children) 52.208.490,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -90702,12 +90674,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>est2025</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>99.02 est2025: parent 0,00 != sum(children) 52.208.490,00 (1 children)</t>
+          <t>99.02 total_2024: parent 400.030,00 != sum(children) 271.389.710,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -90732,12 +90704,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>99.02 est2027: parent 0,00 != sum(children) 17.439.090,00 (1 children)</t>
+          <t>99.02 est2026: parent 0,00 != sum(children) 39.012.850,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -90787,12 +90759,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>07.02.01 est2027: parent 116.000.000,00 != sum(children) 90.000.000,00 (2 children)</t>
+          <t>07.02.01 total_2024: parent 139.644.400,00 != sum(children) 108.940.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -90817,12 +90789,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>est2025</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>07.02.01 est2026: parent 118.700.000,00 != sum(children) 90.000.000,00 (2 children)</t>
+          <t>07.02.01 est2025: parent 116.700.000,00 != sum(children) 90.000.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -90847,12 +90819,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>07.02.01 total_2024: parent 139.644.400,00 != sum(children) 108.940.000,00 (2 children)</t>
+          <t>07.02.01 est2027: parent 116.000.000,00 != sum(children) 90.000.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -90877,12 +90849,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>est2025</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>07.02.01 est2025: parent 116.700.000,00 != sum(children) 90.000.000,00 (2 children)</t>
+          <t>07.02.01 est2026: parent 118.700.000,00 != sum(children) 90.000.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -90907,12 +90879,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>07.02 est2027: parent 116.000.000,00 != sum(children) 142.000.000,00 (4 children)</t>
+          <t>07.02 total_2024: parent 139.644.400,00 != sum(children) 170.348.800,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -90937,12 +90909,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>est2025</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>07.02 est2026: parent 118.700.000,00 != sum(children) 147.400.000,00 (4 children)</t>
+          <t>07.02 est2025: parent 116.700.000,00 != sum(children) 143.400.000,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -90967,12 +90939,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>07.02 total_2024: parent 139.644.400,00 != sum(children) 170.348.800,00 (4 children)</t>
+          <t>07.02 est2027: parent 116.000.000,00 != sum(children) 142.000.000,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -90997,12 +90969,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>est2025</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>07.02 est2025: parent 116.700.000,00 != sum(children) 143.400.000,00 (4 children)</t>
+          <t>07.02 est2026: parent 118.700.000,00 != sum(children) 147.400.000,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -91077,12 +91049,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>11.02 est2027: parent 81.068.000,00 != sum(children) 232.936.000,00 (4 children)</t>
+          <t>11.02 total_2024: parent 101.356.000,00 != sum(children) 283.646.000,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -91107,12 +91079,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>est2025</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>11.02 est2026: parent 79.857.000,00 != sum(children) 235.514.000,00 (4 children)</t>
+          <t>11.02 est2025: parent 78.541.000,00 != sum(children) 229.882.000,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -91137,12 +91109,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>11.02 total_2024: parent 101.356.000,00 != sum(children) 283.646.000,00 (4 children)</t>
+          <t>11.02 est2027: parent 81.068.000,00 != sum(children) 232.936.000,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -91167,12 +91139,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>est2025</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>11.02 est2025: parent 78.541.000,00 != sum(children) 229.882.000,00 (4 children)</t>
+          <t>11.02 est2026: parent 79.857.000,00 != sum(children) 235.514.000,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -91247,12 +91219,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>30.02 est2027: parent 36.760.360,00 != sum(children) 79.707.680,00 (3 children)</t>
+          <t>30.02 total_2024: parent 52.280.000,00 != sum(children) 12.165.560,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -91277,12 +91249,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>est2025</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>30.02 est2026: parent 36.000.000,00 != sum(children) 61.521.740,00 (3 children)</t>
+          <t>30.02 est2025: parent 33.626.120,00 != sum(children) 45.539.240,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -91307,12 +91279,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>30.02 total_2024: parent 52.280.000,00 != sum(children) 12.165.560,00 (3 children)</t>
+          <t>30.02 est2027: parent 36.760.360,00 != sum(children) 79.707.680,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -91337,12 +91309,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>est2025</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>30.02 est2025: parent 33.626.120,00 != sum(children) 45.539.240,00 (3 children)</t>
+          <t>30.02 est2026: parent 36.000.000,00 != sum(children) 61.521.740,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -91417,12 +91389,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>42.02 est2027: parent 7.317.400,00 != sum(children) 14.634.800,00 (4 children)</t>
+          <t>42.02 total_2024: parent 6.414.810,00 != sum(children) 12.829.620,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -91447,12 +91419,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>est2025</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>42.02 est2026: parent 7.033.200,00 != sum(children) 14.066.400,00 (4 children)</t>
+          <t>42.02 est2025: parent 6.728.300,00 != sum(children) 13.456.600,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -91477,12 +91449,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>42.02 total_2024: parent 6.414.810,00 != sum(children) 12.829.620,00 (4 children)</t>
+          <t>42.02 est2027: parent 7.317.400,00 != sum(children) 14.634.800,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -91507,12 +91479,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>est2025</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>42.02 est2025: parent 6.728.300,00 != sum(children) 13.456.600,00 (4 children)</t>
+          <t>42.02 est2026: parent 7.033.200,00 != sum(children) 14.066.400,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -91687,12 +91659,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2025</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>67.02 total_2024: parent 53.899.470,00 != sum(children) 1.360.000,00 (1 children)</t>
+          <t>67.02 est2025: parent 50.625.000,00 != sum(children) 1.348.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -91717,12 +91689,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>est2025</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>67.02 est2025: parent 50.625.000,00 != sum(children) 1.348.000,00 (1 children)</t>
+          <t>67.02 total_2024: parent 53.899.470,00 != sum(children) 1.360.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -91822,12 +91794,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>74.02 total_2024: parent 49.503.480,00 != sum(children) 2.400.000,00 (1 children)</t>
+          <t>74.02 est2027: parent 59.012.000,00 != sum(children) 2.215.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -91852,12 +91824,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>est2025</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>74.02 est2026: parent 56.775.000,00 != sum(children) 2.215.000,00 (1 children)</t>
+          <t>74.02 est2025: parent 54.376.000,00 != sum(children) 2.215.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -91882,12 +91854,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>est2025</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>74.02 est2025: parent 54.376.000,00 != sum(children) 2.215.000,00 (1 children)</t>
+          <t>74.02 total_2024: parent 49.503.480,00 != sum(children) 2.400.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -91912,12 +91884,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>74.02 est2027: parent 59.012.000,00 != sum(children) 2.215.000,00 (1 children)</t>
+          <t>74.02 est2026: parent 56.775.000,00 != sum(children) 2.215.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -91967,12 +91939,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>81.02 total_2024: parent 16.350.000,00 != sum(children) 6.350.000,00 (1 children)</t>
+          <t>81.02 est2027: parent 45.698.000,00 != sum(children) 5.698.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -91997,12 +91969,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>est2025</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>81.02 est2026: parent 40.698.000,00 != sum(children) 5.698.000,00 (1 children)</t>
+          <t>81.02 est2025: parent 35.698.000,00 != sum(children) 5.698.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -92027,12 +91999,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>est2025</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>81.02 est2025: parent 35.698.000,00 != sum(children) 5.698.000,00 (1 children)</t>
+          <t>81.02 total_2024: parent 16.350.000,00 != sum(children) 6.350.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -92057,12 +92029,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>81.02 est2027: parent 45.698.000,00 != sum(children) 5.698.000,00 (1 children)</t>
+          <t>81.02 est2026: parent 40.698.000,00 != sum(children) 5.698.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -92112,12 +92084,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>84.02 total_2024: parent 62.961.130,00 != sum(children) 12.820.000,00 (1 children)</t>
+          <t>84.02 est2027: parent 103.926.300,00 != sum(children) 12.648.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -92142,12 +92114,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>est2025</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>84.02 est2026: parent 104.603.000,00 != sum(children) 17.454.000,00 (1 children)</t>
+          <t>84.02 est2025: parent 95.741.700,00 != sum(children) 12.731.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -92172,12 +92144,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>est2025</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>84.02 est2025: parent 95.741.700,00 != sum(children) 12.731.000,00 (1 children)</t>
+          <t>84.02 total_2024: parent 62.961.130,00 != sum(children) 12.820.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -92202,12 +92174,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>84.02 est2027: parent 103.926.300,00 != sum(children) 12.648.000,00 (1 children)</t>
+          <t>84.02 est2026: parent 104.603.000,00 != sum(children) 17.454.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -92257,12 +92229,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>99.02 total_2024: parent 0,00 != sum(children) 22.930.000,00 (1 children)</t>
+          <t>99.02 est2027: parent 0,00 != sum(children) 20.561.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -92287,12 +92259,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>est2025</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>99.02 est2026: parent 0,00 != sum(children) 25.367.000,00 (1 children)</t>
+          <t>99.02 est2025: parent 0,00 != sum(children) 21.992.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -92317,12 +92289,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>est2025</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>99.02 est2025: parent 0,00 != sum(children) 21.992.000,00 (1 children)</t>
+          <t>99.02 total_2024: parent 0,00 != sum(children) 22.930.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -92347,12 +92319,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>99.02 est2027: parent 0,00 != sum(children) 20.561.000,00 (1 children)</t>
+          <t>99.02 est2026: parent 0,00 != sum(children) 25.367.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -94017,7 +93989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -94043,7 +94015,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -94087,7 +94059,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1736</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="7">
@@ -94097,7 +94069,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1605</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="8">
@@ -94107,7 +94079,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>92.5</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -94143,27 +94115,27 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>Pagini asteptate</t>
+          <t>Linii anexe separate</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Pagini selectate</t>
+          <t>Celule numerice anexe separate</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Pagini procesate</t>
+          <t>Pagini asteptate</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -94173,115 +94145,111 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>PDF complet</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>da</t>
-        </is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>114</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
+          <t>Pagini procesate</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1605</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>% curat</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>92.5</v>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii fara probleme</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>109</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>% curat</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>99</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>Informatii</t>
+          <t>Erori</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Schema publicare</t>
+          <t>Avertismente</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Bundle conversie</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>b01f6d059974cdfdc4c6d52b</t>
-        </is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>SHA-256 sursa</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>bc1d752f85827c7d5a0e0b91deea3587cb09fb3c963a57e71d0364734ee67651</t>
-        </is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Format sursa</t>
+          <t>Bundle conversie</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>66e552ff74adafdacb9ff3e8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>SHA-256 PDF sursa</t>
+          <t>SHA-256 sursa</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -94293,10 +94261,34 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
+          <t>Format sursa</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>bc1d752f85827c7d5a0e0b91deea3587cb09fb3c963a57e71d0364734ee67651</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
           <t>— BUGETUL LOCAL PE ANUL</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>local, pag. 1-114, 1742 linii</t>
         </is>
